--- a/src/test/resources/testData/organisation/stf/stf_organisation_one_valid_row.xlsx
+++ b/src/test/resources/testData/organisation/stf/stf_organisation_one_valid_row.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/Desktop/STOS/Test data/Business/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/workspace/securities-transfer-charge-submissions-ui-tests/src/test/resources/testData/organisation/stf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8091AAA4-DBAD-B242-BA33-44BD3F8E3B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EA874D-7F28-3B47-AB88-364C0A1D96DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,6 @@
     <t>Seller's address - country</t>
   </si>
   <si>
-    <t>Is the business and the seller connected persons?</t>
-  </si>
-  <si>
     <t>Is the business applying for a relief?</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
   <si>
     <t xml:space="preserve">What is the tax rate for this transaction?
 </t>
-  </si>
-  <si>
-    <t>What type of securities are you buying?</t>
   </si>
   <si>
     <t>How many securities are you buying?</t>
@@ -198,9 +192,6 @@
 (Mandatory if shares are the type of security being transfered)</t>
   </si>
   <si>
-    <t>For example; shares (include the share type), interests in underlying securities, loan notes or other debt securities, or other type of securities.</t>
-  </si>
-  <si>
     <t>Enter an amount in GBP. For example, £600.00 or £193.54.
 Enter the amount of consideration given in exchange for these securities as a cash amount.
 You do not need to provide details about conversion or exchange rates, or how valuations of non-monetary items were made.</t>
@@ -307,13 +298,23 @@
   </si>
   <si>
     <t>Seller's name</t>
+  </si>
+  <si>
+    <t>Are the business and the seller connected persons?</t>
+  </si>
+  <si>
+    <t>What class or type of shares are being transfered?</t>
+  </si>
+  <si>
+    <t>For example ordinary, preference or any other share class or type. 
+(Mandatory if shares are the type of security being bought)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -352,6 +353,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -373,18 +380,9 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -394,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -415,7 +413,12 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -642,68 +645,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="N1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="P1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="P1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="R1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S1" t="s">
-        <v>51</v>
-      </c>
-      <c r="T1" t="s">
-        <v>66</v>
-      </c>
-      <c r="U1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="153" x14ac:dyDescent="0.2">
@@ -711,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -735,40 +738,40 @@
         <v>7</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
@@ -794,63 +797,63 @@
     </row>
     <row r="3" spans="1:42" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="R3" s="5" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="S3" s="5"/>
       <c r="T3" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
@@ -877,38 +880,38 @@
     <row r="4" spans="1:42" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D4" s="5">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="J4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N4" s="5">
         <v>12345678</v>
@@ -917,13 +920,13 @@
         <v>46023</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q4" s="5">
         <v>0.5</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="S4" s="5">
         <v>15000</v>
@@ -957,7 +960,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{084FA068-A3C3-7D41-BBD1-F3839A98D4FD}"/>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{1CF0D7C1-FF64-2E41-8CC4-F72AA7373648}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
